--- a/Resources/Completed projects/Completed Projects.xlsx
+++ b/Resources/Completed projects/Completed Projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samsung\Desktop\kivasaglobaltech.com\Resources\Completed projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73003878-F38E-4BEB-BE5C-0018E6987A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB56CD0-0D95-449A-AEA3-8801A82E6836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
   <si>
     <t>Project</t>
   </si>
@@ -109,18 +109,12 @@
     <t>Sabarmati Railway Colony</t>
   </si>
   <si>
-    <t>Indoor and Outdoor Commercial Lighting</t>
-  </si>
-  <si>
     <t>Façade Lighting</t>
   </si>
   <si>
     <t>Street Lighting</t>
   </si>
   <si>
-    <t>Pit Lights</t>
-  </si>
-  <si>
     <t>Indoor lights and Switches</t>
   </si>
   <si>
@@ -166,37 +160,55 @@
     <t>Valsad Loco Shed - Gujarat 2.jpeg</t>
   </si>
   <si>
-    <t>Contact Person</t>
-  </si>
-  <si>
-    <t>Contact Phone</t>
-  </si>
-  <si>
-    <t>Shri R.C. Meena (Sr DE/TRS/BL/WR)</t>
-  </si>
-  <si>
-    <t>Shri K.L. Meena (Sr. DE/POWER/ADI)/WR)</t>
-  </si>
-  <si>
-    <t>Shri Pradeep Meena (Sr. DE/POWER/BRC/WR)</t>
-  </si>
-  <si>
     <t>Yash 63, Navasari Ar. Sanjay Puri</t>
   </si>
   <si>
-    <t>Shri Neel Patel ( Developer)</t>
-  </si>
-  <si>
     <t>Indoor/Outdoor and Façade Lighting Commercial Lighting</t>
   </si>
   <si>
-    <t xml:space="preserve">Shri Satish Panchal </t>
-  </si>
-  <si>
-    <t>Shri Jenish Bhai</t>
-  </si>
-  <si>
     <t>RGBW Façade Lighting</t>
+  </si>
+  <si>
+    <t>Complete Replacement of Overaged Outdoor  Fittings at all facilities of BRC Division.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area Flood Lights, Street Lights, Industrial High bays, Bulkheads, Pit Lights, Well Glass </t>
+  </si>
+  <si>
+    <t>Iconic Road - Navasari</t>
+  </si>
+  <si>
+    <t>Solis Smart Streetlight with 9 Mtr GI Pole and Bracket.</t>
+  </si>
+  <si>
+    <t>Palanpur Railway Station</t>
+  </si>
+  <si>
+    <t>Palanpur railway station.jpg</t>
+  </si>
+  <si>
+    <t>Project Sector</t>
+  </si>
+  <si>
+    <t>Public Transport</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>Roads and Highways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial </t>
+  </si>
+  <si>
+    <t>Indoor, IP54 Platform Lighting Outdoor Commercial Lighting</t>
+  </si>
+  <si>
+    <t>Pit Lighting</t>
   </si>
 </sst>
 </file>
@@ -273,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -287,9 +299,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -572,19 +581,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.796875" customWidth="1"/>
     <col min="2" max="2" width="9.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.3984375" customWidth="1"/>
-    <col min="4" max="4" width="19.796875" customWidth="1"/>
-    <col min="5" max="5" width="16.796875" customWidth="1"/>
-    <col min="6" max="6" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" customWidth="1"/>
+    <col min="5" max="5" width="19.796875" customWidth="1"/>
+    <col min="6" max="6" width="42.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -595,19 +603,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+      <c r="F1" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -618,19 +623,16 @@
         <v>2025</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="3">
-        <v>9724091300</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -641,19 +643,16 @@
         <v>2025</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="3">
-        <v>9724091300</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -664,19 +663,16 @@
         <v>2025</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="3">
-        <v>9724091300</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -687,19 +683,16 @@
         <v>2026</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="3">
-        <v>9724091300</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -710,19 +703,16 @@
         <v>2025</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -733,19 +723,16 @@
         <v>2026</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -756,19 +743,16 @@
         <v>2026</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -778,20 +762,17 @@
       <c r="C9" s="3">
         <v>2026</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>27</v>
+      <c r="D9" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="4">
-        <v>7726049634</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -802,19 +783,16 @@
         <v>2025</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -825,21 +803,18 @@
         <v>2025</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>16</v>
@@ -847,223 +822,258 @@
       <c r="C12" s="3">
         <v>2026</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>28</v>
+      <c r="D12" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="4">
-        <v>9824890290</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2026</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="3">
-        <v>7600018024</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="57" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="3">
-        <v>760018024</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="3">
-        <v>9724093300</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="4">
-        <v>9909953331</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>38</v>
+      <c r="E23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{643ADABD-B8E6-4986-BDFE-50C1E6F354D9}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{572DB179-A0B9-4458-89FD-062C81E3B52A}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{E6746F2C-9D76-439C-953D-621BD577B9E0}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{5C9FECC4-52EB-4682-A091-8FF6F5FE280F}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{5CCFF25D-7817-4B70-AC4F-DBE24D4B4FB2}"/>
-    <hyperlink ref="G7" r:id="rId6" xr:uid="{046385CA-3F2F-4892-8C73-EAF526163E0B}"/>
-    <hyperlink ref="G8" r:id="rId7" xr:uid="{FF72EA06-3A32-4564-BE1D-72135D733098}"/>
-    <hyperlink ref="G14" r:id="rId8" xr:uid="{16A8C3A5-C40B-4994-BEFB-EFB832C48007}"/>
-    <hyperlink ref="G12" r:id="rId9" xr:uid="{874AD7F5-D3B6-4BF5-855C-68AAFD4815B1}"/>
-    <hyperlink ref="G13" r:id="rId10" xr:uid="{E3502F91-8532-4C08-A92D-11DC93E139B8}"/>
-    <hyperlink ref="G10" r:id="rId11" xr:uid="{A2B6CD64-EE6A-4B76-A3E8-8615F3B8D580}"/>
-    <hyperlink ref="G11" r:id="rId12" xr:uid="{A6120DFB-4630-446E-B146-D83BD2BF9EB8}"/>
-    <hyperlink ref="G9" r:id="rId13" xr:uid="{1CDD0146-38CE-4E43-9C23-3D157A0CAA89}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{643ADABD-B8E6-4986-BDFE-50C1E6F354D9}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{572DB179-A0B9-4458-89FD-062C81E3B52A}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{E6746F2C-9D76-439C-953D-621BD577B9E0}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{5C9FECC4-52EB-4682-A091-8FF6F5FE280F}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{5CCFF25D-7817-4B70-AC4F-DBE24D4B4FB2}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{046385CA-3F2F-4892-8C73-EAF526163E0B}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{FF72EA06-3A32-4564-BE1D-72135D733098}"/>
+    <hyperlink ref="F17" r:id="rId8" xr:uid="{16A8C3A5-C40B-4994-BEFB-EFB832C48007}"/>
+    <hyperlink ref="F12" r:id="rId9" xr:uid="{874AD7F5-D3B6-4BF5-855C-68AAFD4815B1}"/>
+    <hyperlink ref="F13" r:id="rId10" xr:uid="{E3502F91-8532-4C08-A92D-11DC93E139B8}"/>
+    <hyperlink ref="F10" r:id="rId11" xr:uid="{A2B6CD64-EE6A-4B76-A3E8-8615F3B8D580}"/>
+    <hyperlink ref="F11" r:id="rId12" xr:uid="{A6120DFB-4630-446E-B146-D83BD2BF9EB8}"/>
+    <hyperlink ref="F9" r:id="rId13" xr:uid="{1CDD0146-38CE-4E43-9C23-3D157A0CAA89}"/>
+    <hyperlink ref="F14" r:id="rId14" xr:uid="{DC0174D8-01D2-4EAF-872A-2C106AE03964}"/>
+    <hyperlink ref="F15:F16" r:id="rId15" display="Under construction.png" xr:uid="{2E4802D3-EB90-4823-B4C1-1BA5C9A88029}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="63" orientation="portrait" r:id="rId14"/>
+  <pageSetup scale="63" orientation="portrait" r:id="rId16"/>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="6" min="2" max="19" man="1"/>
+    <brk id="5" min="2" max="19" man="1"/>
   </colBreaks>
 </worksheet>
 </file>
--- a/Resources/Completed projects/Completed Projects.xlsx
+++ b/Resources/Completed projects/Completed Projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samsung\Desktop\kivasaglobaltech.com\Resources\Completed projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB56CD0-0D95-449A-AEA3-8801A82E6836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B870B0-BD8E-440D-98B9-8F14E73B5C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="59">
   <si>
     <t>Project</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Pit Lighting</t>
+  </si>
+  <si>
+    <t>Sidhpur Railway Station.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1017,10 +1020,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2026</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>51</v>
@@ -1029,7 +1032,7 @@
         <v>43</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -1069,9 +1072,10 @@
     <hyperlink ref="F9" r:id="rId13" xr:uid="{1CDD0146-38CE-4E43-9C23-3D157A0CAA89}"/>
     <hyperlink ref="F14" r:id="rId14" xr:uid="{DC0174D8-01D2-4EAF-872A-2C106AE03964}"/>
     <hyperlink ref="F15:F16" r:id="rId15" display="Under construction.png" xr:uid="{2E4802D3-EB90-4823-B4C1-1BA5C9A88029}"/>
+    <hyperlink ref="F22" r:id="rId16" xr:uid="{236E8BBA-1F66-423B-ADF5-05CB67B015E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="63" orientation="portrait" r:id="rId16"/>
+  <pageSetup scale="63" orientation="portrait" r:id="rId17"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="5" min="2" max="19" man="1"/>
   </colBreaks>
